--- a/forms/trg/Formulir_TRG_farg.xlsx
+++ b/forms/trg/Formulir_TRG_farg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Gagaring Pagalung, SE., M.S., Ak., CA. CMA., CRGP., ASEAN-CPA</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -955,7 +959,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -992,7 +996,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1107,7 +1111,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
